--- a/NECP Scenario/Results/Regional Results/EL53_Capacity.xlsx
+++ b/NECP Scenario/Results/Regional Results/EL53_Capacity.xlsx
@@ -507,25 +507,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1.176538686850932E-11</v>
+        <v>1.737115484392225E-11</v>
       </c>
       <c r="C2">
-        <v>6.160906709401373E-12</v>
+        <v>9.096361643487474E-12</v>
       </c>
       <c r="D2">
-        <v>9.052349325334748E-12</v>
+        <v>1.33654667637399E-11</v>
       </c>
       <c r="E2">
-        <v>1.330097590477158E-11</v>
+        <v>1.963839771704436E-11</v>
       </c>
       <c r="F2">
-        <v>1.954357248706044E-11</v>
+        <v>2.885534006330829E-11</v>
       </c>
       <c r="G2">
-        <v>2.871583634811614E-11</v>
+        <v>4.239782410626645E-11</v>
       </c>
       <c r="H2">
-        <v>1.740389769989079E-10</v>
+        <v>2.569622240217924E-10</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -533,25 +533,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2.479287163974925E-08</v>
+        <v>3.696384856182026E-08</v>
       </c>
       <c r="C3">
-        <v>2.486208299467238E-08</v>
+        <v>3.707669285072255E-08</v>
       </c>
       <c r="D3">
-        <v>5.712417349200485E-08</v>
+        <v>8.242088356895737E-08</v>
       </c>
       <c r="E3">
-        <v>1.143963910696035E-07</v>
+        <v>1.574147456783204E-07</v>
       </c>
       <c r="F3">
-        <v>3.783015114422483E-07</v>
+        <v>4.880959245982137E-07</v>
       </c>
       <c r="G3">
-        <v>2.019217586021261E-06</v>
+        <v>2.799460877611941E-06</v>
       </c>
       <c r="H3">
-        <v>3.91670571310706E-06</v>
+        <v>5.867312737950662E-06</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -562,22 +562,22 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>0.0215706126524029</v>
+        <v>0.0215703690755406</v>
       </c>
       <c r="D4">
-        <v>0.0215706126764197</v>
+        <v>0.0215703691135633</v>
       </c>
       <c r="E4">
-        <v>0.0263446842054892</v>
+        <v>0.0262912862976608</v>
       </c>
       <c r="F4">
-        <v>0.0281324191806335</v>
+        <v>0.0284187755561562</v>
       </c>
       <c r="G4">
-        <v>0.0296805688677039</v>
+        <v>0.0297295423192456</v>
       </c>
       <c r="H4">
-        <v>0.0307653473652015</v>
+        <v>0.0309429451447247</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -692,22 +692,22 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>1.937481176505741E-08</v>
+        <v>2.857568327008226E-08</v>
       </c>
       <c r="D9">
-        <v>2.291185383995137E-08</v>
+        <v>3.479205937694023E-08</v>
       </c>
       <c r="E9">
-        <v>2.373347486486754E-08</v>
+        <v>3.562441732782542E-08</v>
       </c>
       <c r="F9">
-        <v>2.376030947585499E-08</v>
+        <v>3.566239553057662E-08</v>
       </c>
       <c r="G9">
-        <v>2.380503147697879E-08</v>
+        <v>3.572319583280203E-08</v>
       </c>
       <c r="H9">
-        <v>1.090927637889969E-07</v>
+        <v>1.626475293138802E-07</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -793,25 +793,25 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.5130780560053491</v>
+        <v>0.5130780560056396</v>
       </c>
       <c r="C13">
-        <v>0.5130780560070822</v>
+        <v>0.513078056008186</v>
       </c>
       <c r="D13">
-        <v>0.5130780560106218</v>
+        <v>0.5130780560130985</v>
       </c>
       <c r="E13">
-        <v>0.5130780560198875</v>
+        <v>0.51307805602422</v>
       </c>
       <c r="F13">
-        <v>0.5130780560348696</v>
+        <v>0.5130780560422701</v>
       </c>
       <c r="G13">
-        <v>0.5130780560645322</v>
+        <v>0.5130780560801425</v>
       </c>
       <c r="H13">
-        <v>0.5130780563661039</v>
+        <v>0.513078056440872</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -923,25 +923,25 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>1.776812257694772E-08</v>
+        <v>2.641136266998456E-08</v>
       </c>
       <c r="C18">
-        <v>1.777869530663545E-08</v>
+        <v>2.64275750611846E-08</v>
       </c>
       <c r="D18">
-        <v>3.417094279242077E-08</v>
+        <v>5.074596337007744E-08</v>
       </c>
       <c r="E18">
-        <v>7.302575199518381E-08</v>
+        <v>1.036669577981071E-07</v>
       </c>
       <c r="F18">
-        <v>1.984640185995501E-07</v>
+        <v>2.753343994142068E-07</v>
       </c>
       <c r="G18">
-        <v>3.337643561143728E-07</v>
+        <v>5.079297331704859E-07</v>
       </c>
       <c r="H18">
-        <v>1.009412730444895E-06</v>
+        <v>1.5196246430147E-06</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -952,22 +952,22 @@
         <v>0</v>
       </c>
       <c r="C19">
-        <v>9.838924600020376E-09</v>
+        <v>1.489788455103762E-08</v>
       </c>
       <c r="D19">
-        <v>1.484929288160479E-08</v>
+        <v>2.268314875984741E-08</v>
       </c>
       <c r="E19">
-        <v>3.430867252505941E-08</v>
+        <v>5.238148649032446E-08</v>
       </c>
       <c r="F19">
-        <v>1.27192229685582E-07</v>
+        <v>1.85974178516006E-07</v>
       </c>
       <c r="G19">
-        <v>4.949849259900888E-07</v>
+        <v>7.091589249720052E-07</v>
       </c>
       <c r="H19">
-        <v>1.473121269608322E-06</v>
+        <v>2.780677989749322E-06</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1027,25 +1027,25 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>2.905764322912094E-08</v>
+        <v>4.299276911500221E-08</v>
       </c>
       <c r="C22">
-        <v>2.907452779767428E-08</v>
+        <v>4.301778260360453E-08</v>
       </c>
       <c r="D22">
-        <v>2.923008495047287E-08</v>
+        <v>4.325089929283974E-08</v>
       </c>
       <c r="E22">
-        <v>4.014392283152016E-08</v>
+        <v>5.948058410989435E-08</v>
       </c>
       <c r="F22">
-        <v>5.707688985991776E-08</v>
+        <v>8.459937070123628E-08</v>
       </c>
       <c r="G22">
-        <v>8.236757552150055E-08</v>
+        <v>1.217898565579826E-07</v>
       </c>
       <c r="H22">
-        <v>4.984428890059089E-07</v>
+        <v>7.369996454662609E-07</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1160,22 +1160,22 @@
         <v>0</v>
       </c>
       <c r="C27">
-        <v>0.042678254103438</v>
+        <v>1.965464658202664E-06</v>
       </c>
       <c r="D27">
-        <v>0.0426782550406235</v>
+        <v>1.970905079697575E-06</v>
       </c>
       <c r="E27">
-        <v>0.2838887312305765</v>
+        <v>0.2041844750822336</v>
       </c>
       <c r="F27">
-        <v>0.3784523072470857</v>
+        <v>0.3006218185471149</v>
       </c>
       <c r="G27">
-        <v>0.526583161786123</v>
+        <v>0.4128987450818453</v>
       </c>
       <c r="H27">
-        <v>0.5800749543162577</v>
+        <v>0.4842423189620412</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1212,22 +1212,22 @@
         <v>0</v>
       </c>
       <c r="C29">
-        <v>7.886683839794458E-09</v>
+        <v>1.176908389723468E-08</v>
       </c>
       <c r="D29">
-        <v>2.568454551938881E-08</v>
+        <v>4.035922397565055E-08</v>
       </c>
       <c r="E29">
-        <v>7.810670205836093E-08</v>
+        <v>1.452462286216159E-07</v>
       </c>
       <c r="F29">
-        <v>5.806997716546233E-07</v>
+        <v>5.00640446409463E-06</v>
       </c>
       <c r="G29">
-        <v>0.2787400847096664</v>
+        <v>0.2925568462600163</v>
       </c>
       <c r="H29">
-        <v>0.3256564015809789</v>
+        <v>0.3256564014016975</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1264,22 +1264,22 @@
         <v>0</v>
       </c>
       <c r="C31">
-        <v>5.040118570757641E-09</v>
+        <v>7.474536796871706E-09</v>
       </c>
       <c r="D31">
-        <v>6.835257580850802E-09</v>
+        <v>1.026203744691053E-08</v>
       </c>
       <c r="E31">
-        <v>1.125616845787306E-08</v>
+        <v>1.692237279655985E-08</v>
       </c>
       <c r="F31">
-        <v>1.75318356257898E-08</v>
+        <v>2.627975924367502E-08</v>
       </c>
       <c r="G31">
-        <v>2.552606671101278E-08</v>
+        <v>3.784119716246138E-08</v>
       </c>
       <c r="H31">
-        <v>1.467338388778235E-07</v>
+        <v>2.202340675753927E-07</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1316,22 +1316,22 @@
         <v>0</v>
       </c>
       <c r="C33">
-        <v>2.825189278844822E-08</v>
+        <v>4.231609192087257E-08</v>
       </c>
       <c r="D33">
-        <v>3.304279850095495E-08</v>
+        <v>4.956128664750732E-08</v>
       </c>
       <c r="E33">
-        <v>8.660583722487579E-08</v>
+        <v>1.397423075680591E-07</v>
       </c>
       <c r="F33">
-        <v>1.677533528122497E-07</v>
+        <v>2.596253829202961E-07</v>
       </c>
       <c r="G33">
-        <v>1.727871452730592E-07</v>
+        <v>2.613188260836299E-07</v>
       </c>
       <c r="H33">
-        <v>6.667636344653801E-07</v>
+        <v>1.04527798437335E-06</v>
       </c>
     </row>
     <row r="34" spans="1:8">
